--- a/database/excels/staffing/base-seeder.xlsx
+++ b/database/excels/staffing/base-seeder.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/monoland/Platform/monoland/database/excels/staffing/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA2830C9-9A24-3D4A-AB53-929F14F7F7FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F81E1D0-81F0-4B4D-BF0D-9180C14DCB5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" activeTab="5" xr2:uid="{94E1010F-4E68-D749-BBCF-3803F804C4FE}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" activeTab="2" xr2:uid="{94E1010F-4E68-D749-BBCF-3803F804C4FE}"/>
   </bookViews>
   <sheets>
     <sheet name="module" sheetId="2" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="74">
   <si>
     <t>name</t>
   </si>
@@ -228,6 +228,30 @@
   </si>
   <si>
     <t>training</t>
+  </si>
+  <si>
+    <t>Rekom Pegawai</t>
+  </si>
+  <si>
+    <t>Rekomendasi Isi Jabatan</t>
+  </si>
+  <si>
+    <t>staffing-recommend</t>
+  </si>
+  <si>
+    <t>recommend</t>
+  </si>
+  <si>
+    <t>Tugas Belajar</t>
+  </si>
+  <si>
+    <t>staffing-study</t>
+  </si>
+  <si>
+    <t>history_edu</t>
+  </si>
+  <si>
+    <t>study</t>
   </si>
 </sst>
 </file>
@@ -664,7 +688,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CF7F25A-0145-E049-BABB-6C723A859E1D}">
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="18.1640625" customWidth="1"/>
@@ -938,6 +962,64 @@
         <v>0</v>
       </c>
     </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" t="s">
+        <v>66</v>
+      </c>
+      <c r="C10" t="s">
+        <v>67</v>
+      </c>
+      <c r="D10" t="s">
+        <v>68</v>
+      </c>
+      <c r="E10" t="s">
+        <v>69</v>
+      </c>
+      <c r="F10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G10" t="s">
+        <v>69</v>
+      </c>
+      <c r="H10" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I10" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" t="s">
+        <v>70</v>
+      </c>
+      <c r="C11" t="s">
+        <v>70</v>
+      </c>
+      <c r="D11" t="s">
+        <v>71</v>
+      </c>
+      <c r="E11" t="s">
+        <v>72</v>
+      </c>
+      <c r="F11" t="s">
+        <v>26</v>
+      </c>
+      <c r="G11" t="s">
+        <v>73</v>
+      </c>
+      <c r="H11" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I11" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -945,7 +1027,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{462F859E-7489-7142-8B02-E1AE063A22DB}">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="22.33203125" bestFit="1" customWidth="1"/>
@@ -1048,6 +1130,28 @@
         <v>50</v>
       </c>
       <c r="C9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" t="s">
+        <v>68</v>
+      </c>
+      <c r="C10" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" t="s">
+        <v>71</v>
+      </c>
+      <c r="C11" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1096,7 +1200,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{279D8F2B-ACF8-DF40-AE6A-EC20C786574F}">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="33.33203125" customWidth="1"/>
@@ -1202,6 +1306,28 @@
         <v>50</v>
       </c>
     </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" t="s">
+        <v>71</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1209,7 +1335,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2E44C3F-3A12-F647-BCB1-FF7A86E9DA05}">
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="33.33203125" customWidth="1"/>
@@ -1342,6 +1468,34 @@
         <v>17</v>
       </c>
     </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" t="s">
+        <v>68</v>
+      </c>
+      <c r="D10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" t="s">
+        <v>71</v>
+      </c>
+      <c r="D11" t="s">
+        <v>17</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
